--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.138.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.138.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.138" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.138" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.138.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.138.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0138.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0138.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -887,7 +887,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.138.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.138.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.138" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.138" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,8 +431,8 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="49" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="49" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
@@ -609,16 +609,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN :: ä¸€, or other</t>
+          <t>L26: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 :: 一, or other</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L14: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: By a person entitled to haveâ€™a new trustee appointed</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]ORDFRS OF JANUARY 1851.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]ORDFRS OF JANUARY 1851.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L2: isolated marker/symbol line :: 131</t>
@@ -661,7 +665,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -676,14 +680,10 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L31: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN :: ä¸€ ï¼› and</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L57: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” ; and</t>
-        </is>
-      </c>
+          <t>L31: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00, U+FF1B FULLWIDTH SEMICOLON :: 一 ； and</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -739,14 +739,10 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L54: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: (And for further relief; pray subpa Ã¦ na.)</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” day of</t>
-        </is>
-      </c>
+          <t>L72: stray/suspicious non-ASCII glyph(s): U+5730 CJK UNIFIED IDEOGRAPH-5730 | isolated marker/symbol line :: 地</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -762,7 +758,7 @@
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L99: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: f - -----â€”,</t>
+          <t>L99: punctuation artifact: double/multiple hyphen :: f - -----—,</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
@@ -786,12 +782,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -802,19 +798,15 @@
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Order. One is a â€œclaim for specific performance.</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L88: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”except that the words referring to real assets of de- Within the</t>
-        </is>
-      </c>
+          <t>L117: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00, U+FF1B FULLWIDTH SEMICOLON :: 一 ； and</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L84: isolated marker/symbol line :: A</t>
+          <t>L72: stray/suspicious non-ASCII glyph(s): U+5730 CJK UNIFIED IDEOGRAPH-5730 | isolated marker/symbol line :: 地</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
@@ -855,21 +847,13 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L80: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: proceedings may be by claim.â€� The Order in England</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L92: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: judgment creditors, as in the 6th articleâ€”with the addi- orders.</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L107: symbol-only separator/garbage line :: 10.</t>
+          <t>L84: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr"/>
@@ -906,21 +890,13 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L103: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: tion of the following clause (8).â€œA person entitled to</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L99: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: f - -----â€”,</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L131: isolated marker/symbol line :: C</t>
+          <t>L107: symbol-only separator/garbage line :: 10.</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr"/>
@@ -957,17 +933,13 @@
       <c r="G8" s="1" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L105: stray/suspicious non-ASCII glyph(s): U+00B1 PLUS-MINUS SIGN :: Î± na.)</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L147: symbol-only separator/garbage line :: 10.</t>
+          <t>L131: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr"/>
@@ -1004,17 +976,13 @@
       <c r="G9" s="1" t="inlineStr"/>
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L117: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN :: ä¸€ ï¼› and</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L148: isolated marker/symbol line :: 8</t>
+          <t>L147: symbol-only separator/garbage line :: 10.</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr"/>
@@ -1037,12 +1005,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1051,15 +1019,15 @@
       <c r="G10" s="1" t="inlineStr"/>
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr"/>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>L146: stray/suspicious non-ASCII glyph(s): U+00B1 PLUS-MINUS SIGN :: Î± na.)</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
-      <c r="N10" s="1" t="inlineStr"/>
+      <c r="N10" s="1" t="inlineStr">
+        <is>
+          <t>L148: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
       <c r="O10" s="1" t="inlineStr"/>
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr"/>
@@ -1085,7 +1053,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1119,7 +1087,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
